--- a/Assets/Data/Excel/ShopTable.xlsx
+++ b/Assets/Data/Excel/ShopTable.xlsx
@@ -1,34 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763A54AA-6962-4904-9A4A-B2A79F66AD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ShopTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ShopTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>shopId</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>sellCount</t>
+  </si>
+  <si>
+    <t>SHOP_001_01</t>
+  </si>
+  <si>
+    <t>SHOP_001</t>
+  </si>
+  <si>
+    <t>weapon_sword_01</t>
+  </si>
+  <si>
+    <t>SHOP_001_02</t>
+  </si>
+  <si>
+    <t>weapon_sword_02</t>
+  </si>
+  <si>
+    <t>SHOP_001_03</t>
+  </si>
+  <si>
+    <t>weapon_sword_03</t>
+  </si>
+  <si>
+    <t>SHOP_001_04</t>
+  </si>
+  <si>
+    <t>potion_hp_small</t>
+  </si>
+  <si>
+    <t>SHOP_001_05</t>
+  </si>
+  <si>
+    <t>potion_hp_medium</t>
+  </si>
+  <si>
+    <t>SHOP_001_06</t>
+  </si>
+  <si>
+    <t>potion_hp_large</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +117,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,180 +419,138 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>shopId</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>itemId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>sellCount</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SHOP_001_01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>weapon_sword_01</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SHOP_001_02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>weapon_sword_02</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
         <v>300</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SHOP_001_03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>weapon_sword_03</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
         <v>800</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SHOP_001_04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>potion_hp_small</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
         <v>30</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>-1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SHOP_001_05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>potion_hp_medium</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
         <v>70</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>-1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SHOP_001_06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>potion_hp_large</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>150</v>
-      </c>
-      <c r="E7" t="n">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>140</v>
+      </c>
+      <c r="E7">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/ShopTable.xlsx
+++ b/Assets/Data/Excel/ShopTable.xlsx
@@ -15,12 +15,12 @@
   <sheets>
     <sheet name="ShopTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>uniqueId</t>
   </si>
@@ -46,53 +46,125 @@
     <t>weapon_sword_01</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>SHOP_001_02</t>
   </si>
   <si>
     <t>weapon_sword_02</t>
   </si>
   <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>SHOP_001_03</t>
   </si>
   <si>
     <t>weapon_sword_03</t>
   </si>
   <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>SHOP_001_04</t>
   </si>
   <si>
     <t>potion_hp_small</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
     <t>SHOP_001_05</t>
   </si>
   <si>
     <t>potion_hp_medium</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>SHOP_001_06</t>
   </si>
   <si>
     <t>potion_hp_large</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>SHOP_001_07</t>
+  </si>
+  <si>
+    <t>armor_leather</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>SHOP_001_08</t>
+  </si>
+  <si>
+    <t>armor_iron</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>SHOP_001_09</t>
+  </si>
+  <si>
+    <t>ring_magic</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>SHOP_001_10</t>
+  </si>
+  <si>
+    <t>potion_antidote</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>SHOP_001_11</t>
+  </si>
+  <si>
+    <t>potion_stamina</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -116,8 +188,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -420,137 +493,216 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
-        <v>300</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
-        <v>800</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5">
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>70</v>
-      </c>
-      <c r="E6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7">
-        <v>140</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>